--- a/data/trans_dic/P1429-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1429-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,6</t>
+          <t>0,0; 4,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,35</t>
+          <t>0,0; 4,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,86</t>
+          <t>0,09; 0,95</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,2</t>
+          <t>0,0; 3,26</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,42</t>
+          <t>0,14; 1,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 2,03</t>
+          <t>0,16; 2,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -897,12 +897,12 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,95</t>
+          <t>0,16; 1,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,94</t>
+          <t>0,07; 1,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,16</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1007,22 +1007,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,73</t>
+          <t>0,28; 1,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,87</t>
+          <t>0,08; 0,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,09</t>
+          <t>0,23; 1,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,43</t>
+          <t>0,0; 0,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,74</t>
+          <t>0,14; 0,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,81</t>
+          <t>0,13; 0,74</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 1,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,82</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,11; 1,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,35</t>
+          <t>1,55; 4,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,84</t>
+          <t>1,18; 3,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,37</t>
+          <t>0,49; 2,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,2</t>
+          <t>1,02; 2,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,54</t>
+          <t>0,95; 2,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,95</t>
+          <t>0,69; 2,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,47</t>
+          <t>0,34; 1,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,27</t>
+          <t>0,65; 1,5</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,71</t>
+          <t>0,81; 3,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1287,52 +1287,52 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,02</t>
+          <t>0,38; 1,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,03; 11,43</t>
+          <t>6,09; 11,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,68; 10,76</t>
+          <t>5,64; 10,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,83; 6,95</t>
+          <t>2,89; 7,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,1; 8,21</t>
+          <t>5,16; 8,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,78; 7,19</t>
+          <t>3,66; 7,08</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,77</t>
+          <t>2,92; 5,91</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,75</t>
+          <t>1,57; 3,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,93; 4,68</t>
+          <t>2,87; 4,61</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,37</t>
+          <t>1,31; 5,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,91</t>
+          <t>0,8; 2,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,02; 15,66</t>
+          <t>8,81; 15,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,21; 12,6</t>
+          <t>6,29; 12,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,87; 15,38</t>
+          <t>8,31; 15,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,66; 10,76</t>
+          <t>8,21; 12,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,03; 10,18</t>
+          <t>5,95; 10,26</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,25; 6,73</t>
+          <t>3,38; 7,01</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,53; 8,31</t>
+          <t>4,56; 8,19</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,48; 6,54</t>
+          <t>4,95; 7,33</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,49; 8,15</t>
+          <t>2,53; 8,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,46</t>
+          <t>0,0; 5,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,81</t>
+          <t>1,13; 5,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,73</t>
+          <t>1,57; 5,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,15; 18,33</t>
+          <t>9,85; 17,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,75; 17,92</t>
+          <t>10,76; 18,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,77; 15,22</t>
+          <t>7,77; 15,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,03; 18,97</t>
+          <t>14,04; 19,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,4; 13,0</t>
+          <t>7,72; 13,42</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,92; 11,73</t>
+          <t>6,87; 11,66</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,69; 10,15</t>
+          <t>5,52; 10,38</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,41; 12,76</t>
+          <t>9,38; 12,76</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,47</t>
+          <t>0,74; 1,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,44</t>
+          <t>0,06; 0,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,59</t>
+          <t>0,19; 0,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,32</t>
+          <t>0,57; 1,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,59; 5,0</t>
+          <t>3,6; 5,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,36; 4,8</t>
+          <t>3,36; 4,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,85; 4,17</t>
+          <t>2,82; 4,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,67; 5,01</t>
+          <t>4,21; 5,31</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,31; 3,12</t>
+          <t>2,33; 3,1</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,5</t>
+          <t>1,78; 2,51</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,3</t>
+          <t>1,61; 2,28</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,0</t>
+          <t>2,54; 3,19</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>6827</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 22398</t>
+          <t>0; 18178</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>923; 9151</t>
+          <t>918; 9161</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 13620</t>
+          <t>0; 15430</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>907; 8252</t>
+          <t>908; 9105</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 22833</t>
+          <t>0; 25133</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>999; 10463</t>
+          <t>999; 11640</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5904</t>
+          <t>0; 7382</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>950; 12388</t>
+          <t>947; 13054</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1985; 12933</t>
+          <t>2123; 16056</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>943; 12148</t>
+          <t>948; 13251</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>2277</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1726</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>4061</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7407</t>
+          <t>0; 7515</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2494,52 +2494,52 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5376</t>
+          <t>0; 4587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 7616</t>
+          <t>0; 8003</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1967; 11960</t>
+          <t>1965; 11737</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6788</t>
+          <t>0; 6124</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>935; 8501</t>
+          <t>946; 8527</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>462; 4688</t>
+          <t>486; 5142</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3213; 14509</t>
+          <t>3039; 15225</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 5988</t>
+          <t>0; 6819</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1843; 9824</t>
+          <t>1842; 10296</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1183; 8731</t>
+          <t>1594; 9235</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10186</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12840</t>
+          <t>14674</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6337</t>
+          <t>0; 5640</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5067</t>
+          <t>0; 4116</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 7287</t>
+          <t>0; 6828</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 8368</t>
+          <t>733; 8285</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7873; 22416</t>
+          <t>8014; 22619</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8030; 23565</t>
+          <t>7256; 23127</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3208; 15369</t>
+          <t>3160; 14448</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6519; 15585</t>
+          <t>7463; 17966</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10029; 26282</t>
+          <t>9793; 25614</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8333; 23995</t>
+          <t>8423; 24653</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5257; 19035</t>
+          <t>4357; 18322</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6861; 20336</t>
+          <t>9364; 21522</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>5487</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35366</t>
+          <t>39266</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41051</t>
+          <t>44753</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3424; 14335</t>
+          <t>3147; 15234</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4941</t>
+          <t>0; 4935</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6700</t>
+          <t>0; 7766</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2378; 11318</t>
+          <t>2289; 10688</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>24346; 46194</t>
+          <t>24584; 46829</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25450; 48169</t>
+          <t>25249; 47847</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14045; 34520</t>
+          <t>14335; 35154</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>27637; 44467</t>
+          <t>31118; 49861</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29872; 56827</t>
+          <t>28964; 55958</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25756; 50584</t>
+          <t>25614; 51856</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15457; 36546</t>
+          <t>15257; 36346</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>32272; 51541</t>
+          <t>34758; 55824</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>40984</t>
+          <t>44779</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>46939</t>
+          <t>51101</t>
         </is>
       </c>
     </row>
@@ -3108,12 +3108,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3871; 15718</t>
+          <t>3827; 15432</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5300</t>
+          <t>0; 4860</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3123,47 +3123,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3089; 10671</t>
+          <t>3226; 11115</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30945; 53696</t>
+          <t>30200; 53296</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21970; 44608</t>
+          <t>22281; 44554</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33515; 58084</t>
+          <t>31391; 58239</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16113; 65264</t>
+          <t>35890; 55192</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38308; 64683</t>
+          <t>37824; 65236</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21596; 44662</t>
+          <t>22438; 46514</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32289; 59189</t>
+          <t>32444; 58354</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24096; 63585</t>
+          <t>41675; 61706</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>8977</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>69517</t>
+          <t>75886</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>77337</t>
+          <t>84864</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5221; 17101</t>
+          <t>5316; 17473</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 13591</t>
+          <t>0; 13963</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2706; 12355</t>
+          <t>2904; 13038</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4227; 13342</t>
+          <t>4852; 15944</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>33888; 61212</t>
+          <t>32905; 59247</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41678; 69509</t>
+          <t>41750; 70860</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31090; 60895</t>
+          <t>31093; 61228</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>59500; 80431</t>
+          <t>64965; 88281</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>40224; 70706</t>
+          <t>41982; 72968</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44041; 74666</t>
+          <t>43716; 74268</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>37397; 66696</t>
+          <t>36282; 68196</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>66457; 90083</t>
+          <t>72431; 98540</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28317</t>
+          <t>29507</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>160456</t>
+          <t>176773</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>188773</t>
+          <t>206281</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>24797; 48276</t>
+          <t>24124; 46684</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2057; 15112</t>
+          <t>2053; 16314</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6004; 20052</t>
+          <t>6567; 20549</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19725; 45696</t>
+          <t>20019; 43297</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>121146; 169092</t>
+          <t>121541; 169876</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>119238; 170426</t>
+          <t>119540; 170831</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>101099; 147982</t>
+          <t>100010; 146917</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>133684; 182674</t>
+          <t>156533; 197422</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>153714; 207773</t>
+          <t>155055; 206130</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>123147; 174630</t>
+          <t>124345; 175054</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>112228; 159314</t>
+          <t>111519; 158527</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>160015; 212931</t>
+          <t>183894; 231336</t>
         </is>
       </c>
     </row>
